--- a/dist/sample/ccocr_test_plan_FILLED.xlsx
+++ b/dist/sample/ccocr_test_plan_FILLED.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cy/Desktop/CLAUDEs/ccocr/dist/sample/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEBFD22-B29C-094F-A2CA-274E3F08B8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E7F845-C3A7-8A44-8613-F75499FCD05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="1300" windowWidth="36020" windowHeight="18860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="680" yWindow="1300" windowWidth="36020" windowHeight="18860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト計画" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="103">
   <si>
     <t>No.</t>
   </si>
@@ -508,12 +508,16 @@
 従い test 12 - 17 はこの通り行わず、適宜オプションを変えて実行したログを残す</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>[DONE]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -577,6 +581,15 @@
       <name val="Microsoft YaHei"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -671,11 +684,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -692,15 +700,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1478,7 +1489,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1486,13 +1497,13 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="14"/>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="112" customHeight="1">
@@ -1505,10 +1516,10 @@
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="7" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1519,13 +1530,13 @@
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="7" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1539,19 +1550,19 @@
       <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="55" customHeight="1">
@@ -1564,10 +1575,10 @@
       <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1581,21 +1592,21 @@
       <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="55" customHeight="1">
@@ -1608,7 +1619,7 @@
       <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E10" s="3"/>
@@ -1623,10 +1634,10 @@
       <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1641,7 +1652,7 @@
         <v>21</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1656,7 +1667,7 @@
         <v>23</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1670,10 +1681,10 @@
       <c r="C14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="7" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1687,19 +1698,19 @@
       <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="20" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="55" customHeight="1">
@@ -1713,7 +1724,7 @@
         <v>30</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="7" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1783,13 +1794,13 @@
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:6" ht="20" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" ht="55" customHeight="1">
@@ -1867,16 +1878,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="13"/>
+      <c r="D2" s="15"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="10" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1884,10 +1895,10 @@
       <c r="B4" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="10" t="s">
         <v>86</v>
       </c>
       <c r="F4" t="s">
@@ -1898,10 +1909,10 @@
       <c r="B5" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="11" t="s">
         <v>87</v>
       </c>
       <c r="F5" t="s">
@@ -1912,10 +1923,10 @@
       <c r="B6" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="10" t="s">
         <v>87</v>
       </c>
       <c r="F6" t="s">
@@ -1926,10 +1937,10 @@
       <c r="B7" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="10" t="s">
         <v>87</v>
       </c>
       <c r="F7" t="s">
@@ -1940,10 +1951,10 @@
       <c r="B8" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="10" t="s">
         <v>87</v>
       </c>
       <c r="F8" t="s">
@@ -1954,10 +1965,10 @@
       <c r="B10" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="10" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1980,16 +1991,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="13"/>
+      <c r="D2" s="15"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="10" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1997,10 +2008,10 @@
       <c r="B4" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="10" t="s">
         <v>86</v>
       </c>
       <c r="F4" t="s">
@@ -2011,10 +2022,10 @@
       <c r="B5" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="10" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2022,10 +2033,10 @@
       <c r="B6" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="10" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2033,20 +2044,20 @@
       <c r="B7" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="10" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" spans="2:6">
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2062,15 +2073,18 @@
   <dimension ref="A1:AD199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:13">
       <c r="A1">
         <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="M1" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="B2" t="s">
         <v>42</v>
       </c>
@@ -2144,11 +2158,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="184" spans="1:2" s="12" customFormat="1">
-      <c r="A184" s="12">
+    <row r="184" spans="1:2" s="9" customFormat="1">
+      <c r="A184" s="9">
         <v>5</v>
       </c>
-      <c r="B184" s="12" t="s">
+      <c r="B184" s="9" t="s">
         <v>63</v>
       </c>
     </row>

--- a/dist/sample/ccocr_test_plan_FILLED.xlsx
+++ b/dist/sample/ccocr_test_plan_FILLED.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cy/Desktop/CLAUDEs/ccocr/dist/sample/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68F1762-7880-1140-A6B1-281B6A72E7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C16171F-E84B-EB42-B227-DFAE6DC3E165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="1180" windowWidth="36020" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8020" yWindow="1700" windowWidth="36020" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト計画" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="106">
   <si>
     <t>No.</t>
   </si>
@@ -348,14 +348,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>INMORED フォルダに出力されるのは赤枠青枠描画前のものか？</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>今のテストでは空白ページだけg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>input フォルダには設定エクセルがあるフォルダ内のファイルだけをcopyするように変更すべき</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -516,6 +508,22 @@
   </si>
   <si>
     <t>[python -u main.py で対処]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IGNORED フォルダに出力されるのは赤枠青枠描画前のものか？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>今のテストでは空白ページだけ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[誤解 描画あった]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[未実施：Sentry用意したら実装]</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1588,7 +1596,7 @@
         <v>44</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="55" customHeight="1">
@@ -1605,7 +1613,7 @@
         <v>44</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1">
@@ -1644,10 +1652,10 @@
         <v>19</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="55" customHeight="1">
@@ -1662,7 +1670,7 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="55" customHeight="1">
@@ -1677,7 +1685,7 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="55" customHeight="1">
@@ -1691,10 +1699,10 @@
         <v>25</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="55" customHeight="1">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="55" customHeight="1">
@@ -1888,97 +1896,97 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="C2" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D2" s="16"/>
     </row>
     <row r="3" spans="2:6">
       <c r="C3" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="2:6">
       <c r="B4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="2:6">
       <c r="B10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2001,63 +2009,63 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="C2" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D2" s="16"/>
     </row>
     <row r="3" spans="2:6">
       <c r="C3" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="2:6">
       <c r="B4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="2:6">
@@ -2090,7 +2098,7 @@
         <v>41</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2106,7 +2114,7 @@
         <v>45</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -2122,7 +2130,7 @@
         <v>53</v>
       </c>
       <c r="V61" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="15:15">
@@ -2145,7 +2153,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:17">
       <c r="A177">
         <v>4</v>
       </c>
@@ -2153,78 +2161,90 @@
         <v>58</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:17">
       <c r="B178" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:17">
       <c r="B179" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:17">
       <c r="B180" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="182" spans="1:2">
+      <c r="F180" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17">
       <c r="B182" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="184" spans="1:2" s="9" customFormat="1">
+      <c r="O182" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" s="9" customFormat="1">
       <c r="A184" s="9">
         <v>5</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17">
       <c r="B185" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
+        <v>103</v>
+      </c>
+      <c r="J185" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17">
       <c r="A187">
         <v>6</v>
       </c>
       <c r="B187" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17">
       <c r="B188" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
+        <v>64</v>
+      </c>
+      <c r="Q188" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17">
       <c r="A190">
         <v>7</v>
       </c>
       <c r="B190" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17">
+      <c r="B191" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17">
+      <c r="B192" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="B191" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="B192" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="B193" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="B194" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -2232,12 +2252,12 @@
         <v>8</v>
       </c>
       <c r="B196" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="B197" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -2245,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="C198" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -2253,7 +2273,7 @@
         <v>2</v>
       </c>
       <c r="C199" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/dist/sample/ccocr_test_plan_FILLED.xlsx
+++ b/dist/sample/ccocr_test_plan_FILLED.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cy/Desktop/CLAUDEs/ccocr/dist/sample/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C16171F-E84B-EB42-B227-DFAE6DC3E165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004D19BB-61D5-AD4E-A817-ACFB5419CE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8020" yWindow="1700" windowWidth="36020" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="107">
   <si>
     <t>No.</t>
   </si>
@@ -524,6 +524,10 @@
   </si>
   <si>
     <t>[未実施：Sentry用意したら実装]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[DONE 省いた]</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2237,30 +2241,36 @@
         <v>67</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:16">
       <c r="B193" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:16">
       <c r="B194" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="196" spans="1:3">
+      <c r="P194" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16">
       <c r="A196">
         <v>8</v>
       </c>
       <c r="B196" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="197" spans="1:3">
+      <c r="N196" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16">
       <c r="B197" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:16">
       <c r="B198">
         <v>1</v>
       </c>
@@ -2268,7 +2278,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="199" spans="1:3">
+    <row r="199" spans="1:16">
       <c r="B199">
         <v>2</v>
       </c>
